--- a/data/exports/tamil_nadu_synthetic_population_preview.xlsx
+++ b/data/exports/tamil_nadu_synthetic_population_preview.xlsx
@@ -213,7 +213,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-11T16:28:46.747815+00:00</t>
+          <t>2026-09-13T05:30:34.911427+00:00</t>
         </is>
       </c>
     </row>
